--- a/outputs/model_metrics.xlsx
+++ b/outputs/model_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,78 +457,1152 @@
           <t>CV_Std_R2</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Best_CV_R2</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Multiple_Linear_Regression</t>
+          <t>LinearRegression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yield_per_Hectare</t>
+          <t>Yield_per_Plot</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.4525</v>
+        <v>431.0031</v>
       </c>
       <c r="D2" t="n">
-        <v>28.4525</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>497.7158</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.2809</v>
+      </c>
       <c r="F2" t="n">
-        <v>85.69</v>
+        <v>40.35</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yield_per_Hectare</t>
+          <t>Yield_per_Plot</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.4525</v>
+        <v>420.2979</v>
       </c>
       <c r="D3" t="n">
-        <v>28.4525</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>489.2228</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.2375</v>
+      </c>
       <c r="F3" t="n">
-        <v>85.69</v>
+        <v>39.54</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Random_Forest</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yield_per_Hectare</t>
+          <t>Yield_per_Plot</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.4525</v>
+        <v>430.861</v>
       </c>
       <c r="D4" t="n">
-        <v>28.4525</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>497.6265</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.2804</v>
+      </c>
       <c r="F4" t="n">
-        <v>85.69</v>
+        <v>40.35</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Yield_per_Plot</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>427.5526</v>
+      </c>
+      <c r="D5" t="n">
+        <v>494.9941</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.2669</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Yield_per_Plot</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>433.4031</v>
+      </c>
+      <c r="D6" t="n">
+        <v>458.8975</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.08890000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yield_per_Plot</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>435.6227</v>
+      </c>
+      <c r="D7" t="n">
+        <v>466.5275</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.1254</v>
+      </c>
+      <c r="F7" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yield_per_Plot</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>445.5511</v>
+      </c>
+      <c r="D8" t="n">
+        <v>546.9888999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.547</v>
+      </c>
+      <c r="F8" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Plant_Height_cm</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>47.8538</v>
+      </c>
+      <c r="D9" t="n">
+        <v>63.7298</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.1932</v>
+      </c>
+      <c r="F9" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-418.8253</v>
+      </c>
+      <c r="H9" t="n">
+        <v>403.2479</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-418.8253</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Plant_Height_cm</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>47.8141</v>
+      </c>
+      <c r="D10" t="n">
+        <v>63.7163</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.1922</v>
+      </c>
+      <c r="F10" t="n">
+        <v>41.08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-383.1953</v>
+      </c>
+      <c r="H10" t="n">
+        <v>366.8691</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.3384</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{'alpha': 10.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Plant_Height_cm</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>47.7911</v>
+      </c>
+      <c r="D11" t="n">
+        <v>63.7066</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.1916</v>
+      </c>
+      <c r="F11" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-392.2765</v>
+      </c>
+      <c r="H11" t="n">
+        <v>372.458</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.08699999999999999</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{'alpha': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Plant_Height_cm</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>47.7981</v>
+      </c>
+      <c r="D12" t="n">
+        <v>63.7085</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.1917</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-390.4962</v>
+      </c>
+      <c r="H12" t="n">
+        <v>372.3231</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.153</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{'alpha': 1.0, 'l1_ratio': 0.8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Plant_Height_cm</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>47.1412</v>
+      </c>
+      <c r="D13" t="n">
+        <v>63.8384</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.2006</v>
+      </c>
+      <c r="F13" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-351.2725</v>
+      </c>
+      <c r="H13" t="n">
+        <v>452.2941</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1.6028</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{'max_depth': 3, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Plant_Height_cm</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>47.3347</v>
+      </c>
+      <c r="D14" t="n">
+        <v>63.82</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.1994</v>
+      </c>
+      <c r="F14" t="n">
+        <v>39.82</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-688.6728000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1099.8047</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.8613</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{'max_depth': 2, 'n_estimators': 50}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Plant_Height_cm</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>47.3103</v>
+      </c>
+      <c r="D15" t="n">
+        <v>63.8172</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.1992</v>
+      </c>
+      <c r="F15" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-907.4468000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1137.9144</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-6.49</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{'max_depth': 3, 'n_estimators': 50}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Plant_Height_cm</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>47.2234</v>
+      </c>
+      <c r="D16" t="n">
+        <v>63.8797</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.2035</v>
+      </c>
+      <c r="F16" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-7.9031</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10.7869</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{'C': 10.0, 'epsilon': 0.01}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SPAD</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>49.0044</v>
+      </c>
+      <c r="D17" t="n">
+        <v>59.2454</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.4888</v>
+      </c>
+      <c r="F17" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-3987.1645</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4555.605</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3987.1645</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SPAD</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>64.4932</v>
+      </c>
+      <c r="D18" t="n">
+        <v>74.1707</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.3334</v>
+      </c>
+      <c r="F18" t="n">
+        <v>127.81</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-845.0334</v>
+      </c>
+      <c r="H18" t="n">
+        <v>726.6532</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-401.8627</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{'alpha': 10.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SPAD</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>49.7564</v>
+      </c>
+      <c r="D19" t="n">
+        <v>59.8486</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.5193</v>
+      </c>
+      <c r="F19" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-3869.2014</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4407.6724</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-2355.2931</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{'alpha': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SPAD</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>61.4327</v>
+      </c>
+      <c r="D20" t="n">
+        <v>71.0478</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.141</v>
+      </c>
+      <c r="F20" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1020.9797</v>
+      </c>
+      <c r="H20" t="n">
+        <v>912.2974</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-520.5348</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>{'alpha': 1.0, 'l1_ratio': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SPAD</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>120.2575</v>
+      </c>
+      <c r="D21" t="n">
+        <v>128.8277</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-6.0395</v>
+      </c>
+      <c r="F21" t="n">
+        <v>197.76</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-991.4897999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1383.2352</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-279.0527</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>{'max_depth': 5, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SPAD</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>112.9582</v>
+      </c>
+      <c r="D22" t="n">
+        <v>144.7257</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-7.8841</v>
+      </c>
+      <c r="F22" t="n">
+        <v>186.98</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1700.72</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2453.1152</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-637.1147999999999</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>{'max_depth': 2, 'n_estimators': 50}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SPAD</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>112.8784</v>
+      </c>
+      <c r="D23" t="n">
+        <v>144.6031</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-7.869</v>
+      </c>
+      <c r="F23" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1694.7531</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2442.5019</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-642.6704999999999</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>{'max_depth': 5, 'n_estimators': 50}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SPAD</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>36.0324</v>
+      </c>
+      <c r="D24" t="n">
+        <v>56.6622</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.3618</v>
+      </c>
+      <c r="F24" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.903</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5921999999999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.4372</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>{'C': 0.1, 'epsilon': 0.01}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9003</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.4205</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.4205</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.8474</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-3.4205</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.5449</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.1127</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.502</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.9484</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.6438</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>{'alpha': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.1913</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.7375</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.4074</v>
+      </c>
+      <c r="F27" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.5637</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.5424</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.8002</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>{'alpha': 0.01}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.0927</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.6492</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.2679</v>
+      </c>
+      <c r="F28" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.4098</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.5658</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.6756</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.1634</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.7751</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.4689</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.8173</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.1693</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.089</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>{'max_depth': 5, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1.0732</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.6811</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.3176</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1.1291</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.0234</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1261</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>{'max_depth': 3, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9411</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.6517</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.2719</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.2251</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6413</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.4399</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>{'max_depth': 3, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.1366</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.8192</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.5427999999999999</v>
+      </c>
+      <c r="F32" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.6857</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.8428</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.7527</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>{'C': 1.0, 'epsilon': 0.1}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/model_metrics.xlsx
+++ b/outputs/model_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>431.0031</v>
+        <v>389.7884</v>
       </c>
       <c r="D2" t="n">
-        <v>497.7158</v>
+        <v>481.2096</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2809</v>
+        <v>-0.1973</v>
       </c>
       <c r="F2" t="n">
-        <v>40.35</v>
+        <v>37.92</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -512,16 +512,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>420.2979</v>
+        <v>392.5491</v>
       </c>
       <c r="D3" t="n">
-        <v>489.2228</v>
+        <v>478.1578</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2375</v>
+        <v>-0.1822</v>
       </c>
       <c r="F3" t="n">
-        <v>39.54</v>
+        <v>37.91</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>430.861</v>
+        <v>389.802</v>
       </c>
       <c r="D4" t="n">
-        <v>497.6265</v>
+        <v>481.1881</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2804</v>
+        <v>-0.1972</v>
       </c>
       <c r="F4" t="n">
-        <v>40.35</v>
+        <v>37.92</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>427.5526</v>
+        <v>390.6859</v>
       </c>
       <c r="D5" t="n">
-        <v>494.9941</v>
+        <v>480.2533</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2669</v>
+        <v>-0.1926</v>
       </c>
       <c r="F5" t="n">
-        <v>40.09</v>
+        <v>37.92</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -608,16 +608,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>433.4031</v>
+        <v>404.5621</v>
       </c>
       <c r="D6" t="n">
-        <v>458.8975</v>
+        <v>467.2311</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1288</v>
       </c>
       <c r="F6" t="n">
-        <v>38.1</v>
+        <v>37.88</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>435.6227</v>
+        <v>422.1858</v>
       </c>
       <c r="D7" t="n">
-        <v>466.5275</v>
+        <v>564.4687</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1254</v>
+        <v>-0.6475</v>
       </c>
       <c r="F7" t="n">
-        <v>38.68</v>
+        <v>42.79</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>445.5511</v>
+        <v>439.7701</v>
       </c>
       <c r="D8" t="n">
-        <v>546.9888999999999</v>
+        <v>545.693</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.547</v>
+        <v>-0.5397</v>
       </c>
       <c r="F8" t="n">
-        <v>43.21</v>
+        <v>42.9</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -700,29 +700,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Plant_Height_cm</t>
+          <t>Yield_per_Hectare</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47.8538</v>
+        <v>91.8109</v>
       </c>
       <c r="D9" t="n">
-        <v>63.7298</v>
+        <v>111.1959</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1932</v>
+        <v>-0.0206</v>
       </c>
       <c r="F9" t="n">
-        <v>41.15</v>
+        <v>4356.19</v>
       </c>
       <c r="G9" t="n">
-        <v>-418.8253</v>
+        <v>-36.9935</v>
       </c>
       <c r="H9" t="n">
-        <v>403.2479</v>
+        <v>61.5095</v>
       </c>
       <c r="I9" t="n">
-        <v>-418.8253</v>
+        <v>-36.9935</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -738,33 +738,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Plant_Height_cm</t>
+          <t>Yield_per_Hectare</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47.8141</v>
+        <v>90.881</v>
       </c>
       <c r="D10" t="n">
-        <v>63.7163</v>
+        <v>110.7651</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1922</v>
+        <v>-0.0127</v>
       </c>
       <c r="F10" t="n">
-        <v>41.08</v>
+        <v>4241.52</v>
       </c>
       <c r="G10" t="n">
-        <v>-383.1953</v>
+        <v>-32.811</v>
       </c>
       <c r="H10" t="n">
-        <v>366.8691</v>
+        <v>53.2531</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3384</v>
+        <v>-3.8031</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{'alpha': 10.0}</t>
+          <t>{'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -776,33 +776,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plant_Height_cm</t>
+          <t>Yield_per_Hectare</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.7911</v>
+        <v>91.7188</v>
       </c>
       <c r="D11" t="n">
-        <v>63.7066</v>
+        <v>111.1634</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1916</v>
+        <v>-0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>41.03</v>
+        <v>4343.21</v>
       </c>
       <c r="G11" t="n">
-        <v>-392.2765</v>
+        <v>-36.734</v>
       </c>
       <c r="H11" t="n">
-        <v>372.458</v>
+        <v>61.0021</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-3.8027</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{'alpha': 1.0}</t>
+          <t>{'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -814,33 +814,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plant_Height_cm</t>
+          <t>Yield_per_Hectare</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>47.7981</v>
+        <v>91.2212</v>
       </c>
       <c r="D12" t="n">
-        <v>63.7085</v>
+        <v>110.929</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1917</v>
+        <v>-0.0157</v>
       </c>
       <c r="F12" t="n">
-        <v>41.05</v>
+        <v>4282.34</v>
       </c>
       <c r="G12" t="n">
-        <v>-390.4962</v>
+        <v>-34.3435</v>
       </c>
       <c r="H12" t="n">
-        <v>372.3231</v>
+        <v>56.278</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.153</v>
+        <v>-3.8038</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{'alpha': 1.0, 'l1_ratio': 0.8}</t>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.8}</t>
         </is>
       </c>
     </row>
@@ -852,33 +852,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Plant_Height_cm</t>
+          <t>Yield_per_Hectare</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47.1412</v>
+        <v>40.8028</v>
       </c>
       <c r="D13" t="n">
-        <v>63.8384</v>
+        <v>63.6501</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2006</v>
+        <v>0.6656</v>
       </c>
       <c r="F13" t="n">
-        <v>39.35</v>
+        <v>467.01</v>
       </c>
       <c r="G13" t="n">
-        <v>-351.2725</v>
+        <v>-34.7003</v>
       </c>
       <c r="H13" t="n">
-        <v>452.2941</v>
+        <v>50.5496</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6028</v>
+        <v>-7.4378</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{'max_depth': 3, 'n_estimators': 100}</t>
+          <t>{'max_depth': 5, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -890,29 +890,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Plant_Height_cm</t>
+          <t>Yield_per_Hectare</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>47.3347</v>
+        <v>31.0065</v>
       </c>
       <c r="D14" t="n">
-        <v>63.82</v>
+        <v>46.894</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1994</v>
+        <v>0.8185</v>
       </c>
       <c r="F14" t="n">
-        <v>39.82</v>
+        <v>162.89</v>
       </c>
       <c r="G14" t="n">
-        <v>-688.6728000000001</v>
+        <v>-36.1822</v>
       </c>
       <c r="H14" t="n">
-        <v>1099.8047</v>
+        <v>66.4738</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8613</v>
+        <v>-9.0372</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -928,33 +928,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Plant_Height_cm</t>
+          <t>Yield_per_Hectare</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47.3103</v>
+        <v>30.6482</v>
       </c>
       <c r="D15" t="n">
-        <v>63.8172</v>
+        <v>46.3029</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1992</v>
+        <v>0.823</v>
       </c>
       <c r="F15" t="n">
-        <v>39.77</v>
+        <v>139.52</v>
       </c>
       <c r="G15" t="n">
-        <v>-907.4468000000001</v>
+        <v>-41.0983</v>
       </c>
       <c r="H15" t="n">
-        <v>1137.9144</v>
+        <v>57.6124</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.49</v>
+        <v>-25.3124</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{'max_depth': 3, 'n_estimators': 50}</t>
+          <t>{'max_depth': 2, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -966,33 +966,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Plant_Height_cm</t>
+          <t>Yield_per_Hectare</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>47.2234</v>
+        <v>80.9987</v>
       </c>
       <c r="D16" t="n">
-        <v>63.8797</v>
+        <v>132.8822</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2035</v>
+        <v>-0.4575</v>
       </c>
       <c r="F16" t="n">
-        <v>39.49</v>
+        <v>601.73</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.9031</v>
+        <v>-0.7731</v>
       </c>
       <c r="H16" t="n">
-        <v>10.7869</v>
+        <v>0.2594</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0194</v>
+        <v>-0.337</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>{'C': 10.0, 'epsilon': 0.01}</t>
+          <t>{'C': 1.0, 'epsilon': 0.1}</t>
         </is>
       </c>
     </row>
@@ -1004,29 +1004,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SPAD</t>
+          <t>Plant_Height_cm</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49.0044</v>
+        <v>0.3209</v>
       </c>
       <c r="D17" t="n">
-        <v>59.2454</v>
+        <v>0.3211</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4888</v>
+        <v>0.9752</v>
       </c>
       <c r="F17" t="n">
-        <v>91.05</v>
+        <v>0.77</v>
       </c>
       <c r="G17" t="n">
-        <v>-3987.1645</v>
+        <v>-0.8794</v>
       </c>
       <c r="H17" t="n">
-        <v>4555.605</v>
+        <v>1.7581</v>
       </c>
       <c r="I17" t="n">
-        <v>-3987.1645</v>
+        <v>-0.8794</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1042,29 +1042,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SPAD</t>
+          <t>Plant_Height_cm</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>64.4932</v>
+        <v>0.1275</v>
       </c>
       <c r="D18" t="n">
-        <v>74.1707</v>
+        <v>0.1403</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3334</v>
+        <v>0.9953</v>
       </c>
       <c r="F18" t="n">
-        <v>127.81</v>
+        <v>0.31</v>
       </c>
       <c r="G18" t="n">
-        <v>-845.0334</v>
+        <v>-0.7206</v>
       </c>
       <c r="H18" t="n">
-        <v>726.6532</v>
+        <v>1.4626</v>
       </c>
       <c r="I18" t="n">
-        <v>-401.8627</v>
+        <v>0.6236</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1080,29 +1080,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SPAD</t>
+          <t>Plant_Height_cm</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>49.7564</v>
+        <v>0.1664</v>
       </c>
       <c r="D19" t="n">
-        <v>59.8486</v>
+        <v>0.1844</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5193</v>
+        <v>0.9918</v>
       </c>
       <c r="F19" t="n">
-        <v>92.83</v>
+        <v>0.41</v>
       </c>
       <c r="G19" t="n">
-        <v>-3869.2014</v>
+        <v>-0.8492</v>
       </c>
       <c r="H19" t="n">
-        <v>4407.6724</v>
+        <v>1.7706</v>
       </c>
       <c r="I19" t="n">
-        <v>-2355.2931</v>
+        <v>0.6162</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1118,33 +1118,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SPAD</t>
+          <t>Plant_Height_cm</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>61.4327</v>
+        <v>0.1621</v>
       </c>
       <c r="D20" t="n">
-        <v>71.0478</v>
+        <v>0.1744</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.141</v>
+        <v>0.9927</v>
       </c>
       <c r="F20" t="n">
-        <v>120.23</v>
+        <v>0.4</v>
       </c>
       <c r="G20" t="n">
-        <v>-1020.9797</v>
+        <v>-0.8257</v>
       </c>
       <c r="H20" t="n">
-        <v>912.2974</v>
+        <v>1.6999</v>
       </c>
       <c r="I20" t="n">
-        <v>-520.5348</v>
+        <v>0.6119</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>{'alpha': 1.0, 'l1_ratio': 0.2}</t>
+          <t>{'alpha': 1.0, 'l1_ratio': 0.8}</t>
         </is>
       </c>
     </row>
@@ -1156,33 +1156,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SPAD</t>
+          <t>Plant_Height_cm</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>120.2575</v>
+        <v>1.4151</v>
       </c>
       <c r="D21" t="n">
-        <v>128.8277</v>
+        <v>1.4915</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.0395</v>
+        <v>0.464</v>
       </c>
       <c r="F21" t="n">
-        <v>197.76</v>
+        <v>3.44</v>
       </c>
       <c r="G21" t="n">
-        <v>-991.4897999999999</v>
+        <v>-0.9972</v>
       </c>
       <c r="H21" t="n">
-        <v>1383.2352</v>
+        <v>1.845</v>
       </c>
       <c r="I21" t="n">
-        <v>-279.0527</v>
+        <v>0.5127</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'n_estimators': 100}</t>
+          <t>{'max_depth': 7, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -1194,33 +1194,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SPAD</t>
+          <t>Plant_Height_cm</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>112.9582</v>
+        <v>2.7611</v>
       </c>
       <c r="D22" t="n">
-        <v>144.7257</v>
+        <v>2.8707</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.8841</v>
+        <v>-0.9855</v>
       </c>
       <c r="F22" t="n">
-        <v>186.98</v>
+        <v>6.7</v>
       </c>
       <c r="G22" t="n">
-        <v>-1700.72</v>
+        <v>-0.6309</v>
       </c>
       <c r="H22" t="n">
-        <v>2453.1152</v>
+        <v>1.453</v>
       </c>
       <c r="I22" t="n">
-        <v>-637.1147999999999</v>
+        <v>0.2968</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>{'max_depth': 2, 'n_estimators': 50}</t>
+          <t>{'max_depth': 3, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -1232,33 +1232,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SPAD</t>
+          <t>Plant_Height_cm</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>112.8784</v>
+        <v>1.4626</v>
       </c>
       <c r="D23" t="n">
-        <v>144.6031</v>
+        <v>1.5072</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.869</v>
+        <v>0.4527</v>
       </c>
       <c r="F23" t="n">
-        <v>186.8</v>
+        <v>3.46</v>
       </c>
       <c r="G23" t="n">
-        <v>-1694.7531</v>
+        <v>-5.7779</v>
       </c>
       <c r="H23" t="n">
-        <v>2442.5019</v>
+        <v>4.9829</v>
       </c>
       <c r="I23" t="n">
-        <v>-642.6704999999999</v>
+        <v>-0.9398</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'n_estimators': 50}</t>
+          <t>{'max_depth': 3, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -1270,33 +1270,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SPAD</t>
+          <t>Plant_Height_cm</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>36.0324</v>
+        <v>2.4346</v>
       </c>
       <c r="D24" t="n">
-        <v>56.6622</v>
+        <v>3.0818</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3618</v>
+        <v>-1.2881</v>
       </c>
       <c r="F24" t="n">
-        <v>29.05</v>
+        <v>5.61</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.903</v>
+        <v>-4.4066</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5921999999999999</v>
+        <v>4.4738</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4372</v>
+        <v>0.435</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>{'C': 0.1, 'epsilon': 0.01}</t>
+          <t>{'C': 10.0, 'epsilon': 0.1}</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1308,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shoot_Biomass_g</t>
+          <t>SPAD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9003</v>
+        <v>2.4275</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4205</v>
+        <v>2.6241</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0594</v>
+        <v>0.3325</v>
       </c>
       <c r="F25" t="n">
-        <v>13.25</v>
+        <v>4.87</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.4205</v>
+        <v>-8.0877</v>
       </c>
       <c r="H25" t="n">
-        <v>3.8474</v>
+        <v>9.456300000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.4205</v>
+        <v>-8.0877</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1346,33 +1346,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shoot_Biomass_g</t>
+          <t>SPAD</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9893999999999999</v>
+        <v>2.4758</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5449</v>
+        <v>2.664</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1127</v>
+        <v>0.312</v>
       </c>
       <c r="F26" t="n">
-        <v>14.51</v>
+        <v>4.98</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.502</v>
+        <v>-6.508</v>
       </c>
       <c r="H26" t="n">
-        <v>2.9484</v>
+        <v>9.2409</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6438</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>{'alpha': 1.0}</t>
+          <t>{'alpha': 10.0}</t>
         </is>
       </c>
     </row>
@@ -1384,33 +1384,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shoot_Biomass_g</t>
+          <t>SPAD</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.1913</v>
+        <v>2.665</v>
       </c>
       <c r="D27" t="n">
-        <v>1.7375</v>
+        <v>2.8401</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4074</v>
+        <v>0.2181</v>
       </c>
       <c r="F27" t="n">
-        <v>17.07</v>
+        <v>5.4</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.5637</v>
+        <v>-7.2803</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5424</v>
+        <v>9.248100000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8002</v>
+        <v>-0.3742</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01}</t>
+          <t>{'alpha': 1.0}</t>
         </is>
       </c>
     </row>
@@ -1422,33 +1422,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shoot_Biomass_g</t>
+          <t>SPAD</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.0927</v>
+        <v>2.5762</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6492</v>
+        <v>2.7535</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2679</v>
+        <v>0.2651</v>
       </c>
       <c r="F28" t="n">
-        <v>15.84</v>
+        <v>5.2</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.4098</v>
+        <v>-6.8832</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5658</v>
+        <v>9.209099999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6756</v>
+        <v>-0.3766</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'l1_ratio': 0.5}</t>
+          <t>{'alpha': 1.0, 'l1_ratio': 0.8}</t>
         </is>
       </c>
     </row>
@@ -1460,33 +1460,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shoot_Biomass_g</t>
+          <t>SPAD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.1634</v>
+        <v>3.0215</v>
       </c>
       <c r="D29" t="n">
-        <v>1.7751</v>
+        <v>3.2279</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4689</v>
+        <v>-0.01</v>
       </c>
       <c r="F29" t="n">
-        <v>16.93</v>
+        <v>6.06</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.8173</v>
+        <v>-5.1263</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1693</v>
+        <v>9.987299999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.089</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'n_estimators': 100}</t>
+          <t>{'max_depth': 3, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1498,33 +1498,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shoot_Biomass_g</t>
+          <t>SPAD</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.0732</v>
+        <v>3.8166</v>
       </c>
       <c r="D30" t="n">
-        <v>1.6811</v>
+        <v>4.6777</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3176</v>
+        <v>-1.121</v>
       </c>
       <c r="F30" t="n">
-        <v>15.75</v>
+        <v>7.75</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.1291</v>
+        <v>-6.7825</v>
       </c>
       <c r="H30" t="n">
-        <v>2.0234</v>
+        <v>13.091</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1261</v>
+        <v>-2.2154</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>{'max_depth': 3, 'n_estimators': 100}</t>
+          <t>{'max_depth': 2, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -1536,33 +1536,33 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shoot_Biomass_g</t>
+          <t>SPAD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9411</v>
+        <v>2.5517</v>
       </c>
       <c r="D31" t="n">
-        <v>1.6517</v>
+        <v>3.3789</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2719</v>
+        <v>-0.1067</v>
       </c>
       <c r="F31" t="n">
-        <v>14.35</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2251</v>
+        <v>-6.5823</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6413</v>
+        <v>13.1988</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4399</v>
+        <v>-0.799</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>{'max_depth': 3, 'n_estimators': 100}</t>
+          <t>{'max_depth': 2, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -1574,31 +1574,335 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>SPAD</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3.4966</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.6788</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.3119</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-9.9863</v>
+      </c>
+      <c r="H32" t="n">
+        <v>16.3792</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.5631</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>{'C': 10.0, 'epsilon': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Shoot_Biomass_g</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1.1366</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1.8192</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-0.5427999999999999</v>
-      </c>
-      <c r="F32" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="G32" t="n">
-        <v>-0.6857</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.8428</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-0.7527</v>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="C33" t="n">
+        <v>0.8545</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-3.2637</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.5413</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-3.2637</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.4964</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-2.5041</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.8483</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.6107</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>{'alpha': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1.1913</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.7375</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.4074</v>
+      </c>
+      <c r="F35" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-2.5905</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.3972</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.8006</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>{'alpha': 0.01}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1.0873</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.6311</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.2403</v>
+      </c>
+      <c r="F36" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-2.434</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.503</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.7042</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1.1457</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.7443</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.4185</v>
+      </c>
+      <c r="F37" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.8236</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.1777</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.0866</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>{'max_depth': 5, 'n_estimators': 50}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1.0731</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.6811</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.3175</v>
+      </c>
+      <c r="F38" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-1.1323</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.0305</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>{'max_depth': 3, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.9411</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.6517</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.2719</v>
+      </c>
+      <c r="F39" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.2291</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6476</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.4399</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>{'max_depth': 3, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Shoot_Biomass_g</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.8278</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.5575</v>
+      </c>
+      <c r="F40" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.6817</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.8411999999999999</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.7509</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>{'C': 1.0, 'epsilon': 0.1}</t>
         </is>
